--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_291_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_291_R30.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1631</v>
+        <v>5.2982</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1262</v>
+        <v>4.3621</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0369</v>
+        <v>0.9361</v>
       </c>
       <c r="G2" t="n">
         <v>4.5949</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4292</v>
+        <v>-0.2941</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3176</v>
+        <v>0.2168</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3943</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9381</v>
+        <v>1.9901</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0299</v>
+        <v>0.6196</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9082</v>
+        <v>1.3705</v>
       </c>
       <c r="G3" t="n">
         <v>2.1669</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0185</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9709</v>
+        <v>-0.3811</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9893</v>
+        <v>0.4516</v>
       </c>
       <c r="V3" t="n">
         <v>1.6083</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6297</v>
+        <v>1.6962</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3397</v>
+        <v>-0.5756</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9694</v>
+        <v>2.2718</v>
       </c>
       <c r="G4" t="n">
         <v>0.8764999999999999</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1955</v>
+        <v>-0.1289</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0351</v>
+        <v>-0.2711</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1603</v>
+        <v>0.1421</v>
       </c>
       <c r="V4" t="n">
         <v>3.5002</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8407</v>
+        <v>1.2104</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1419</v>
+        <v>0.7407</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9825</v>
+        <v>0.4697</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0149</v>
+        <v>1.0141</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9411</v>
+        <v>0.0805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0737</v>
+        <v>0.9336</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1404</v>
+        <v>1.3795</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9564</v>
+        <v>0.9144</v>
       </c>
       <c r="L5" t="n">
-        <v>0.184</v>
+        <v>0.465</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1255</v>
+        <v>-0.3654</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0152</v>
+        <v>-0.8339</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1103</v>
+        <v>0.4685</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3825</v>
+        <v>-0.7883</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8259</v>
+        <v>-0.2317</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5566</v>
+        <v>-0.5566</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8608</v>
+        <v>2.1444</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7886</v>
+        <v>2.1444</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6241</v>
+        <v>-0.1007</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7183</v>
+        <v>-0.1074</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3871</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3333</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2072</v>
+        <v>0.3815</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1502</v>
+        <v>-0.1574</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1509</v>
+        <v>-0.2898</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0007</v>
+        <v>0.1324</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0141</v>
+        <v>-1.1392</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0805</v>
+        <v>-0.8114</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9336</v>
+        <v>-0.3279</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3795</v>
+        <v>0.1976</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9144</v>
+        <v>0.0504</v>
       </c>
       <c r="L7" t="n">
-        <v>0.465</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3654</v>
+        <v>-1.3369</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8339</v>
+        <v>-0.8618</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4685</v>
+        <v>-0.4751</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5515</v>
+        <v>-0.4639</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8486</v>
+        <v>0.286</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8215</v>
+        <v>-0.0235</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0271</v>
+        <v>0.3095</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1073</v>
+        <v>-0.2875</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4077</v>
+        <v>-0.9675</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3004</v>
+        <v>0.6801</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1392</v>
+        <v>2.0149</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8114</v>
+        <v>1.9411</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3279</v>
+        <v>0.0737</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1976</v>
+        <v>2.1404</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0504</v>
+        <v>1.9564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1472</v>
+        <v>0.184</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3369</v>
+        <v>-0.1255</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8618</v>
+        <v>-0.0152</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4751</v>
+        <v>-0.1103</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3361</v>
+        <v>0.2544</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1415</v>
+        <v>0.0002</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4775</v>
+        <v>0.2541</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.8608</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.508</v>
+        <v>-0.3907</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3728</v>
+        <v>-0.4907</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1352</v>
+        <v>0.1</v>
       </c>
       <c r="G9" t="n">
         <v>0.6206</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2631</v>
+        <v>0.3804</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4208</v>
+        <v>0.3029</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1577</v>
+        <v>0.0775</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4706</v>
+        <v>-1.2518</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7291</v>
+        <v>-0.6111</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7415</v>
+        <v>-0.6407</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7776</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1568</v>
+        <v>0.0619</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0668</v>
+        <v>0.0512</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0891</v>
+        <v>-1.8361</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2755</v>
+        <v>-1.9217</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1864</v>
+        <v>0.0856</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2302</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2983</v>
+        <v>0.5513</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5149</v>
+        <v>-0.161</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8132</v>
+        <v>0.7123</v>
       </c>
       <c r="V11" t="n">
         <v>0.3943</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.170900000000001</v>
+        <v>6.170700000000002</v>
       </c>
       <c r="E12" t="n">
         <v>0.7585999999999995</v>
       </c>
       <c r="F12" t="n">
-        <v>5.412199999999999</v>
+        <v>5.412100000000001</v>
       </c>
       <c r="G12" t="n">
         <v>7.7538</v>
@@ -1360,7 +1360,7 @@
         <v>-1.1638</v>
       </c>
       <c r="I12" t="n">
-        <v>8.917299999999999</v>
+        <v>8.917300000000001</v>
       </c>
       <c r="J12" t="n">
         <v>15.2814</v>
@@ -1390,19 +1390,19 @@
         <v>13.9172</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0017</v>
+        <v>1.0016</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8436</v>
+        <v>-0.8435</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8451</v>
+        <v>1.845</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5339</v>
+        <v>5.533900000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>8.356199999999999</v>
+        <v>8.356200000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-2.8223</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.445</v>
+        <v>7.4115</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6359</v>
+        <v>6.5795</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8091</v>
+        <v>0.832</v>
       </c>
       <c r="G13" t="n">
         <v>6.5326</v>
@@ -1468,13 +1468,13 @@
         <v>3.0154</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7266</v>
+        <v>0.2399</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.187</v>
+        <v>-0.2434</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4604</v>
+        <v>0.4832</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6403</v>
+        <v>4.7297</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6455</v>
+        <v>1.4096</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9949</v>
+        <v>3.3202</v>
       </c>
       <c r="G14" t="n">
         <v>3.2596</v>
@@ -1546,13 +1546,13 @@
         <v>3.4793</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7095</v>
+        <v>-0.6201</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4086</v>
+        <v>-0.6445</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3009</v>
+        <v>0.0244</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5931</v>
+        <v>3.1448</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1752</v>
+        <v>-0.0607</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4179</v>
+        <v>3.2055</v>
       </c>
       <c r="G15" t="n">
         <v>0.5124</v>
@@ -1624,13 +1624,13 @@
         <v>3.0154</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0627</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3857</v>
+        <v>0.1498</v>
       </c>
       <c r="U15" t="n">
-        <v>0.677</v>
+        <v>0.4646</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4271</v>
+        <v>2.3256</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7614</v>
+        <v>2.5255</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3343</v>
+        <v>-0.1999</v>
       </c>
       <c r="G16" t="n">
         <v>2.5895</v>
@@ -1702,13 +1702,13 @@
         <v>3.0154</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.036</v>
+        <v>-0.1375</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0272</v>
+        <v>-0.2631</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.1256</v>
       </c>
       <c r="V16" t="n">
         <v>-1.7501</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0263</v>
+        <v>0.453</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2403</v>
+        <v>-1.0044</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2665</v>
+        <v>1.4574</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7075</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7481</v>
+        <v>-0.3213</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.076</v>
+        <v>0.1149</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2394</v>
+        <v>-0.5605</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1568</v>
+        <v>0.2478</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.8083</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6983</v>
+        <v>-0.7178</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2797</v>
+        <v>-0.3865</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4187</v>
+        <v>-0.3312</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7191</v>
+        <v>0.3225</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0672</v>
+        <v>0.2857</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7863</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9792</v>
+        <v>-1.0402</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3469</v>
+        <v>-0.6722</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6323</v>
+        <v>-0.368</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.995</v>
+        <v>0.1573</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5623</v>
+        <v>0.1573</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4327</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5605</v>
+        <v>-0.7659</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2478</v>
+        <v>-0.2796</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8083</v>
+        <v>-0.4863</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7178</v>
+        <v>-1.8088</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3865</v>
+        <v>-0.293</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3312</v>
+        <v>-1.5158</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3225</v>
+        <v>0.1999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2857</v>
+        <v>0.5581</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-0.3581</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0402</v>
+        <v>-2.0087</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6722</v>
+        <v>-0.851</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.368</v>
+        <v>-1.1577</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1573</v>
+        <v>-0.5808</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1573</v>
+        <v>-0.4795</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.1013</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0747</v>
+        <v>-0.9465</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3975</v>
+        <v>-0.6286</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6772</v>
+        <v>-0.3179</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8088</v>
+        <v>-1.6983</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.293</v>
+        <v>-0.2797</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5158</v>
+        <v>-1.4187</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1999</v>
+        <v>-0.7191</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5581</v>
+        <v>0.0672</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3581</v>
+        <v>-0.7863</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0087</v>
+        <v>-0.9792</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.851</v>
+        <v>-0.3469</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1577</v>
+        <v>-0.6323</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8895999999999999</v>
+        <v>0.288</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5975</v>
+        <v>0.0905</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2921</v>
+        <v>0.1975</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1189</v>
+        <v>-1.5235</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2698</v>
+        <v>0.798</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3888</v>
+        <v>-2.3216</v>
       </c>
       <c r="G21" t="n">
         <v>-2.7444</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9296</v>
+        <v>0.525</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8259</v>
+        <v>0.3541</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1037</v>
+        <v>0.1709</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5674</v>
+        <v>-4.4158</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1943</v>
+        <v>-3.0764</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.373</v>
+        <v>-1.3394</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5927</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.583</v>
+        <v>-0.4314</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0631</v>
+        <v>-5.3332</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5552</v>
+        <v>-5.027</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5078</v>
+        <v>-0.3062</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4794</v>
@@ -2248,13 +2248,13 @@
         <v>2.5515</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2565</v>
+        <v>-0.0136</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3778</v>
+        <v>-0.094</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1212</v>
+        <v>0.0804</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.6786</v>
+        <v>-9.903700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.6037</v>
+        <v>-6.896</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.075</v>
+        <v>-3.0077</v>
       </c>
       <c r="G24" t="n">
         <v>-5.8991</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7099</v>
+        <v>0.065</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8136</v>
+        <v>-0.1059</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1037</v>
+        <v>0.1709</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7501</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.170800000000002</v>
+        <v>-5.384499999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.412199999999999</v>
+        <v>-5.412299999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7585999999999999</v>
+        <v>0.02780000000000005</v>
       </c>
       <c r="G25" t="n">
         <v>-7.753899999999998</v>
@@ -2404,13 +2404,13 @@
         <v>22.03570000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0016</v>
+        <v>-0.2151</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.8451</v>
+        <v>-1.845</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8435999999999999</v>
+        <v>1.6298</v>
       </c>
       <c r="V25" t="n">
         <v>-5.5339</v>
